--- a/backend/data/difference_analysis.xlsx
+++ b/backend/data/difference_analysis.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X41"/>
+  <dimension ref="A1:Z40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,563 +448,609 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>se1_평균</t>
+          <t>독11_평균</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>se1_표준편차</t>
+          <t>독11_표준편차</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>se2_평균</t>
+          <t>독12_평균</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>se2_표준편차</t>
+          <t>독12_표준편차</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>se3_평균</t>
+          <t>독22_평균</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>se3_표준편차</t>
+          <t>독22_표준편차</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>직무만족_평균</t>
+          <t>독23_평균</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>직무만족_표준편차</t>
+          <t>독23_표준편차</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>정서적몰입_평균</t>
+          <t>종1_평균</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>정서적몰입_표준편차</t>
+          <t>종1_표준편차</t>
         </is>
       </c>
       <c r="M3" s="1" t="inlineStr">
         <is>
-          <t>자기효능감_평균</t>
+          <t>매12_평균</t>
         </is>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>자기효능감_표준편차</t>
+          <t>매12_표준편차</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>새 1_평균</t>
+          <t>매13_평균</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
         <is>
-          <t>새 1_표준편차</t>
+          <t>매13_표준편차</t>
         </is>
       </c>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>새 2_평균</t>
+          <t>매14_평균</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr">
         <is>
-          <t>새 2_표준편차</t>
+          <t>매14_표준편차</t>
         </is>
       </c>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>새 3_평균</t>
+          <t>매2_평균</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr">
         <is>
-          <t>새 3_표준편차</t>
+          <t>매2_표준편차</t>
         </is>
       </c>
       <c r="U3" s="1" t="inlineStr">
         <is>
-          <t>새 4_평균</t>
+          <t>조11_평균</t>
         </is>
       </c>
       <c r="V3" s="1" t="inlineStr">
         <is>
-          <t>새 4_표준편차</t>
+          <t>조11_표준편차</t>
         </is>
       </c>
       <c r="W3" s="1" t="inlineStr">
         <is>
-          <t>새 5_평균</t>
+          <t>조12_평균</t>
         </is>
       </c>
       <c r="X3" s="1" t="inlineStr">
         <is>
-          <t>새 5_표준편차</t>
+          <t>조12_표준편차</t>
+        </is>
+      </c>
+      <c r="Y3" s="1" t="inlineStr">
+        <is>
+          <t>조132_평균</t>
+        </is>
+      </c>
+      <c r="Z3" s="1" t="inlineStr">
+        <is>
+          <t>조132_표준편차</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>성별</t>
+          <t>귀하의연령은</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.022</t>
+          <t>3.260</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>0.411</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.796</t>
+          <t>4.106</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>0.685</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4.213</t>
+          <t>4.368</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>0.640</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.161</t>
+          <t>4.401</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.758</t>
+          <t>0.627</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3.712</t>
+          <t>4.121</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>0.654</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>4.175</t>
+          <t>4.040</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>0.690</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>4.060</t>
+          <t>4.008</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>0.715</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>3.858</t>
+          <t>4.285</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.781</t>
+          <t>0.715</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>4.024</t>
+          <t>4.040</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.700</t>
+          <t>0.736</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2.568</t>
+          <t>3.850</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>1.058</t>
+          <t>0.791</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>3.852</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>0.839</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>3.711</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.748</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>성별</t>
+          <t>귀하의연령은</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.167</t>
+          <t>3.221</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>0.344</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3.804</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.648</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4.359</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.565</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4.367</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.556</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>3.937</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.612</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>3.852</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>4.033</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.560</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>4.179</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>0.632</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3.712</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.760</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>4.151</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.647</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4.183</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.608</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>3.729</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.687</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>4.061</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>4.059</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0.620</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>3.895</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0.576</t>
-        </is>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>3.990</t>
+          <t>4.014</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.560</t>
+          <t>0.569</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.566</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>0.673</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.727</t>
+          <t>3.406</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.679</t>
+          <t>0.725</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>3.722</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.535</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>성별</t>
+          <t>귀하의연령은</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t-value(p)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.511(.133)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>3.215</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.350</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.782(.435)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>4.019</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.648</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.724(.470)</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>4.335</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.639</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.240(.811)</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>4.386</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.599</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.158(.874)</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>4.096</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.664</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1.333(.184)</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>3.927</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.669</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.009(.992)</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
+          <t>4.076</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.602</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-0.413(.681)</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
+          <t>4.215</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.592</t>
+        </is>
+      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.408(.684)</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>4.076</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.015(.988)</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
+          <t>3.785</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.762</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.370(.173)</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
+          <t>3.434</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.807</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>3.772</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.633</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>연령</t>
+          <t>귀하의연령은</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>F-value(p)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.125</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.682</t>
-        </is>
-      </c>
+          <t>0.599(.550)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.792</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.930</t>
-        </is>
-      </c>
+          <t>9.066***(.000)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.076</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.602</t>
-        </is>
-      </c>
+          <t>0.073(.929)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.109</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.516</t>
-        </is>
-      </c>
+          <t>0.137(.872)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3.617</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0.764</t>
-        </is>
-      </c>
+          <t>3.897*(.021)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>4.240</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0.587</t>
-        </is>
-      </c>
+          <t>3.576*†(.030)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>3.883</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0.720</t>
-        </is>
-      </c>
+          <t>0.289†(.750)</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>3.708</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0.675</t>
-        </is>
-      </c>
+          <t>0.999†(.370)</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>4.042</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>0.657</t>
-        </is>
-      </c>
+          <t>0.280†(.756)</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2.808</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
+          <t>0.314†(.731)</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.885</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0.585</t>
-        </is>
-      </c>
+          <t>1.678(.188)</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.243†(.785)</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>연령</t>
+          <t>귀하의학력은</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1014,119 +1060,129 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.982</t>
+          <t>3.256</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>0.370</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.559</t>
+          <t>4.082</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.920</t>
+          <t>0.683</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.191</t>
+          <t>4.388</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>0.603</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.136</t>
+          <t>4.414</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.895</t>
+          <t>0.599</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3.441</t>
+          <t>4.127</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.978</t>
+          <t>0.676</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>4.129</t>
+          <t>4.035</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.679</t>
+          <t>0.711</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>4.029</t>
+          <t>4.049</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.806</t>
+          <t>0.707</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3.676</t>
+          <t>4.306</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>0.738</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>3.947</t>
+          <t>4.084</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>0.747</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2.506</t>
+          <t>3.893</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>0.831</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>3.846</t>
+          <t>3.597</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>0.857</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>3.750</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.779</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>연령</t>
+          <t>귀하의학력은</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1136,77 +1192,77 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.028</t>
+          <t>3.232</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>0.379</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.644</t>
+          <t>3.916</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>0.640</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.910</t>
+          <t>4.366</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.702</t>
+          <t>0.575</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.050</t>
+          <t>4.393</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.650</t>
+          <t>0.548</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>3.556</t>
+          <t>3.999</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>0.623</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3.945</t>
+          <t>3.900</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>0.603</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>3.976</t>
+          <t>4.027</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>0.574</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3.768</t>
+          <t>4.186</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1216,39 +1272,49 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>3.812</t>
+          <t>4.030</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>0.582</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2.568</t>
+          <t>3.798</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>0.671</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3.730</t>
+          <t>3.416</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.701</t>
+          <t>0.741</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>3.723</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0.549</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>연령</t>
+          <t>귀하의학력은</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1258,319 +1324,345 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.184</t>
+          <t>3.194</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>0.343</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.812</t>
+          <t>3.817</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>0.742</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.281</t>
+          <t>4.258</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>0.716</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.227</t>
+          <t>4.275</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>0.704</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3.823</t>
+          <t>3.957</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>0.621</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>3.837</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.580</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>4.013</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0.637</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>4.183</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0.725</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3.946</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>0.654</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>4.161</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.586</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>4.093</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0.653</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>3.956</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0.552</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>4.098</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0.540</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2.586</t>
+          <t>3.672</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>0.712</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3.748</t>
+          <t>3.367</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.632</t>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>3.694</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.597</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>연령</t>
+          <t>귀하의학력은</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>F-value(p)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.149</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.702</t>
-        </is>
-      </c>
+          <t>0.585(.557)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.754</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.850</t>
-        </is>
-      </c>
+          <t>4.069*(.018)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.200</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.756</t>
-        </is>
-      </c>
+          <t>0.995(.370)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.225</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.721</t>
-        </is>
-      </c>
+          <t>0.907†(.406)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3.854</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.734</t>
-        </is>
-      </c>
+          <t>2.174(.115)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>4.037</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.807</t>
-        </is>
-      </c>
+          <t>2.479†(.087)</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>4.140</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.754</t>
-        </is>
-      </c>
+          <t>0.071†(.932)</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4.009</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0.715</t>
-        </is>
-      </c>
+          <t>1.338†(.265)</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>3.989</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0.735</t>
-        </is>
-      </c>
+          <t>0.842†(.433)</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2.480</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.992</t>
-        </is>
-      </c>
+          <t>1.796†(.169)</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
-          <t>3.746</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0.827</t>
-        </is>
-      </c>
+          <t>2.816(.061)</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0.148†(.862)</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>연령</t>
+          <t>귀하의직업은복수로체크가능</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>F-value(p)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.813(.518)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>3.238</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.372</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.865(.486)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>3.909</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.649</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.936*(.021)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>4.374</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.615</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.816(.516)</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>4.378</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.612</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.956*(.020)</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>4.039</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0.633</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1.325(.261)</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>3.914</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.638</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.882(.475)</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
+          <t>4.054</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.635</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2.789*(.027)</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
+          <t>4.217</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0.641</t>
+        </is>
+      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2.076(.084)</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>4.016</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>0.636</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0.590(.670)</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr"/>
+          <t>3.776</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0.699</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.345(.847)</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr"/>
+          <t>3.407</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0.774</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>3.712</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>0.603</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>학력</t>
+          <t>귀하의직업은복수로체크가능</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1580,119 +1672,129 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.911</t>
+          <t>3.292</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>0.394</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3.541</t>
+          <t>4.050</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.885</t>
+          <t>0.648</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4.051</t>
+          <t>4.450</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>0.478</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4.463</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.486</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>4.135</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.586</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>4.000</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.620</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>4.094</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.576</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>4.275</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0.554</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>4.088</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>0.542</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>3.750</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
           <t>0.798</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3.982</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0.733</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>3.545</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>0.800</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>3.976</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0.784</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>3.845</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>0.813</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>3.686</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>0.747</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>3.861</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>0.678</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>2.475</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>0.896</t>
-        </is>
-      </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>3.597</t>
+          <t>3.550</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>0.751</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>3.879</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>0.535</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>학력</t>
+          <t>귀하의직업은복수로체크가능</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1702,119 +1804,129 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4.174</t>
+          <t>3.261</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>0.301</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3.738</t>
+          <t>3.783</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.785</t>
+          <t>0.671</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.179</t>
+          <t>4.043</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>0.620</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.206</t>
+          <t>4.065</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.629</t>
+          <t>0.609</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>3.740</t>
+          <t>3.696</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.748</t>
+          <t>0.652</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>4.120</t>
+          <t>3.620</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.597</t>
+          <t>0.543</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>4.072</t>
+          <t>3.739</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.628</t>
+          <t>0.530</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>3.865</t>
+          <t>3.739</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>0.619</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>3.988</t>
+          <t>3.641</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.555</t>
+          <t>0.543</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2.682</t>
+          <t>3.420</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.961</t>
+          <t>0.515</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>3.788</t>
+          <t>3.076</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0.677</t>
+          <t>0.576</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>3.449</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>0.533</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>학력</t>
+          <t>귀하의직업은복수로체크가능</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1824,32 +1936,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4.276</t>
+          <t>3.217</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.582</t>
+          <t>0.322</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3.973</t>
+          <t>3.860</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.680</t>
+          <t>0.684</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.297</t>
+          <t>4.343</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>0.580</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1859,2148 +1971,2278 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.536</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>3.905</t>
+          <t>3.926</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>0.661</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>4.201</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>0.632</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>4.292</t>
+          <t>4.058</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>0.567</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>4.151</t>
+          <t>4.198</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.542</t>
+          <t>0.629</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>4.189</t>
+          <t>4.073</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.563</t>
+          <t>0.639</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2.473</t>
+          <t>3.810</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.944</t>
+          <t>0.735</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>3.932</t>
+          <t>3.451</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>0.776</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>3.696</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>0.616</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>학력</t>
+          <t>귀하의직업은복수로체크가능</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>F-value(p)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.357**(.002)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>3.239</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.436</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.975**(.003)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>4.160</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.662</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.805(.062)</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>4.429</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.633</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6.974**(.001)</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>4.462</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.628</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4.638*(.010)</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>4.208</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0.639</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2.405(.092)</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>4.154</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0.652</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>8.780***(.000)</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
+          <t>3.994</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0.743</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>11.219***(.000)</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
+          <t>4.372</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0.758</t>
+        </is>
+      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>6.128**(.002)</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>4.090</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>0.752</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1.766(.173)</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr"/>
+          <t>3.957</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0.799</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>4.832**(.009)</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr"/>
+          <t>3.628</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>0.824</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>3.733</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>0.766</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>월평균소득</t>
+          <t>귀하의직업은복수로체크가능</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4.101</t>
+          <t>3.182</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>0.348</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3.687</t>
+          <t>3.932</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.896</t>
+          <t>0.728</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4.117</t>
+          <t>4.284</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>0.642</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4.123</t>
+          <t>4.409</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>3.576</t>
+          <t>4.009</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.793</t>
+          <t>0.604</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3.989</t>
+          <t>3.943</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.651</t>
+          <t>0.598</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>3.890</t>
+          <t>4.074</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>0.567</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3.773</t>
+          <t>4.250</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.632</t>
+          <t>0.576</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>3.922</t>
+          <t>4.085</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>0.622</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2.701</t>
+          <t>3.924</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.922</t>
+          <t>0.704</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>3.765</t>
+          <t>3.540</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>0.837</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>3.837</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>0.647</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>월평균소득</t>
+          <t>귀하의직업은복수로체크가능</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>F-value(p)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4.100</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.735</t>
-        </is>
-      </c>
+          <t>0.447†(.815)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3.623</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0.822</t>
-        </is>
-      </c>
+          <t>2.425*(.035)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.100</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0.733</t>
-        </is>
-      </c>
+          <t>1.821(.108)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4.171</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>0.705</t>
-        </is>
-      </c>
+          <t>1.836(.105)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>3.718</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>0.737</t>
-        </is>
-      </c>
+          <t>3.206**(.008)</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>4.072</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>0.728</t>
-        </is>
-      </c>
+          <t>3.739**(.003)</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>4.082</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>0.718</t>
-        </is>
-      </c>
+          <t>1.247(.286)</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>3.865</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>0.680</t>
-        </is>
-      </c>
+          <t>3.493**(.004)</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>3.988</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>0.641</t>
-        </is>
-      </c>
+          <t>2.648*†(.026)</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2.443</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>0.868</t>
-        </is>
-      </c>
+          <t>2.288*(.045)</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
-          <t>3.763</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>0.737</t>
-        </is>
-      </c>
+          <t>2.165(.057)</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2.165†(.062)</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>월평균소득</t>
+          <t>귀하의월소득수준은</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4.179</t>
+          <t>3.240</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>0.399</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3.907</t>
+          <t>4.033</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>0.670</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.253</t>
+          <t>4.341</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.599</t>
+          <t>0.647</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4.213</t>
+          <t>4.363</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>0.653</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3.807</t>
+          <t>4.076</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>0.641</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>4.136</t>
+          <t>3.996</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>0.651</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>4.172</t>
+          <t>4.011</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>0.677</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>3.931</t>
+          <t>4.247</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>0.712</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>4.041</t>
+          <t>4.062</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.535</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2.566</t>
+          <t>3.864</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.981</t>
+          <t>0.768</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>3.677</t>
+          <t>3.545</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>0.702</t>
+          <t>0.811</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>3.744</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0.706</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>월평균소득</t>
+          <t>귀하의월소득수준은</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4.128</t>
+          <t>3.226</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>0.345</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3.898</t>
+          <t>3.901</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>0.654</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4.326</t>
+          <t>4.335</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>0.572</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.218</t>
+          <t>4.376</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.545</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3.843</t>
+          <t>3.973</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.748</t>
+          <t>0.668</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>4.269</t>
+          <t>3.894</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>4.106</t>
+          <t>4.026</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>0.574</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>4.030</t>
+          <t>4.168</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>0.605</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>4.094</t>
+          <t>3.991</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>0.614</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2.689</t>
+          <t>3.762</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1.072</t>
+          <t>0.701</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>3.894</t>
+          <t>3.415</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>0.701</t>
+          <t>0.780</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>3.693</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>0.591</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>월평균소득</t>
+          <t>귀하의월소득수준은</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>F-value(p)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.188(.905)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>3.189</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.349</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2.401(.068)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>3.774</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0.669</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.762(.155)</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>4.425</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.592</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.271(.847)</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>4.453</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.512</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.453(.228)</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>3.992</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0.571</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.725(.162)</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>3.821</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0.664</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.978(.117)</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
+          <t>4.061</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>0.647</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.598(.190)</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
+          <t>4.226</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0.640</t>
+        </is>
+      </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.841(.472)</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>4.024</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>0.555</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.421(.237)</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr"/>
+          <t>3.799</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0.746</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.830(.478)</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr"/>
+          <t>3.392</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>0.735</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>3.736</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>0.544</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>재직기간</t>
+          <t>귀하의월소득수준은</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.116</t>
+          <t>3.389</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>0.348</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>4.194</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.935</t>
+          <t>0.788</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4.059</t>
+          <t>4.528</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.577</t>
+          <t>0.499</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4.032</t>
+          <t>4.444</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>0.539</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>3.568</t>
+          <t>4.289</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.770</t>
+          <t>0.567</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>4.141</t>
+          <t>4.014</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>0.546</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>3.826</t>
+          <t>4.208</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.661</t>
+          <t>0.509</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>3.787</t>
+          <t>4.500</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.626</t>
+          <t>0.514</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>3.961</t>
+          <t>4.194</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>0.539</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2.800</t>
+          <t>3.741</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.918</t>
+          <t>0.642</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>3.790</t>
+          <t>3.375</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>0.698</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>3.852</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>0.574</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>재직기간</t>
+          <t>귀하의월소득수준은</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>F-value(p)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.762</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0.820</t>
-        </is>
-      </c>
+          <t>1.358(.255)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3.592</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0.825</t>
-        </is>
-      </c>
+          <t>3.245*(.022)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3.865</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0.650</t>
-        </is>
-      </c>
+          <t>0.807(.490)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4.048</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>0.567</t>
-        </is>
-      </c>
+          <t>0.459†(.712)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>3.523</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>0.796</t>
-        </is>
-      </c>
+          <t>1.776(.151)</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>3.827</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>0.692</t>
-        </is>
-      </c>
+          <t>1.426(.235)</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3.977</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>0.828</t>
-        </is>
-      </c>
+          <t>0.583(.626)</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3.754</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>0.677</t>
-        </is>
-      </c>
+          <t>2.213†(.094)</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>3.808</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>0.547</t>
-        </is>
-      </c>
+          <t>0.880†(.456)</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2.423</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>0.873</t>
-        </is>
-      </c>
+          <t>0.620(.602)</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
-          <t>3.731</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>0.790</t>
-        </is>
-      </c>
+          <t>1.089(.354)</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>0.494†(.687)</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>재직기간</t>
+          <t>귀하가거주하는지역은</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>4.067</t>
+          <t>3.230</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.697</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.713</t>
+          <t>3.959</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>0.623</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>4.106</t>
+          <t>4.373</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.583</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4.108</t>
+          <t>4.417</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>0.576</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.527</t>
+          <t>4.002</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.749</t>
+          <t>0.619</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>4.129</t>
+          <t>3.924</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>0.579</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>3.920</t>
+          <t>4.032</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>0.559</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>3.627</t>
+          <t>4.177</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>0.598</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>3.987</t>
+          <t>4.029</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.458</t>
+          <t>0.616</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2.547</t>
+          <t>3.823</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.861</t>
+          <t>0.686</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>3.742</t>
+          <t>3.445</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>0.737</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>3.720</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>0.575</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>재직기간</t>
+          <t>귀하가거주하는지역은</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>4.123</t>
+          <t>3.252</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>0.376</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3.719</t>
+          <t>3.985</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>0.717</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4.132</t>
+          <t>4.376</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>0.642</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4.105</t>
+          <t>4.393</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>0.603</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>3.653</t>
+          <t>4.098</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.874</t>
+          <t>0.668</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>4.024</t>
+          <t>3.983</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>0.695</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>4.130</t>
+          <t>4.057</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.654</t>
+          <t>0.694</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>3.982</t>
+          <t>4.293</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>0.702</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>3.979</t>
+          <t>4.068</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>0.691</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2.561</t>
+          <t>3.824</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.971</t>
+          <t>0.786</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>3.833</t>
+          <t>3.511</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>0.832</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>3.750</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>0.698</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>재직기간</t>
+          <t>귀하가거주하는지역은</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>4.188</t>
+          <t>3.131</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>0.378</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3.758</t>
+          <t>3.714</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.725</t>
+          <t>0.644</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>4.261</t>
+          <t>4.125</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>0.422</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4.225</t>
+          <t>4.089</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>0.510</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>3.795</t>
+          <t>3.779</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>0.529</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>4.121</t>
+          <t>3.652</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>0.520</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>4.071</t>
+          <t>3.848</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>0.511</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>3.927</t>
+          <t>4.036</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>0.637</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>4.014</t>
+          <t>3.830</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>0.518</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2.567</t>
+          <t>3.631</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>0.900</t>
+          <t>0.631</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>3.656</t>
+          <t>3.295</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>0.727</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>3.613</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>0.558</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>재직기간</t>
+          <t>귀하가거주하는지역은</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>F-value(p)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4.203</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>0.726</t>
-        </is>
-      </c>
+          <t>1.337(.264)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3.825</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>0.859</t>
-        </is>
-      </c>
+          <t>2.003(.136)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4.296</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>0.722</t>
-        </is>
-      </c>
+          <t>4.202*†(.018)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4.329</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>0.715</t>
-        </is>
-      </c>
+          <t>4.920**†(.010)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>3.943</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>0.764</t>
-        </is>
-      </c>
+          <t>4.337*†(.016)</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>4.206</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>0.814</t>
-        </is>
-      </c>
+          <t>4.535*†(.014)</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>4.197</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>0.769</t>
-        </is>
-      </c>
+          <t>1.897†(.157)</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>3.959</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>0.746</t>
-        </is>
-      </c>
+          <t>2.710†(.073)</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>4.108</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>0.737</t>
-        </is>
-      </c>
+          <t>2.360†(.101)</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2.524</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>1.048</t>
-        </is>
-      </c>
+          <t>1.181†(.312)</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
-          <t>3.873</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>0.794</t>
-        </is>
-      </c>
+          <t>1.069(.344)</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>0.689†(.505)</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>재직기간</t>
+          <t>귀하의종교는</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>F-value(p)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.763(.120)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>3.229</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0.371</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.358(.877)</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>3.944</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0.673</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.169(.058)</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>4.355</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0.606</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.477(.197)</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>4.377</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.593</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2.358*(.040)</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
+          <t>4.029</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0.646</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1.371(.235)</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>3.924</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0.637</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>1.648(.147)</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr"/>
+          <t>4.024</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>0.629</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.832(.107)</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
+          <t>4.212</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>0.971(.436)</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
+          <t>4.024</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>0.648</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0.528(.755)</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr"/>
+          <t>3.798</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0.733</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>0.841(.521)</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr"/>
+          <t>3.460</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>0.787</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>3.718</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>0.635</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>직위</t>
+          <t>귀하의종교는</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>4.292</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>0.338</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4.054</t>
+          <t>4.308</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>0.663</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4.263</t>
+          <t>4.423</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>0.607</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4.399</t>
+          <t>4.577</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.532</t>
+          <t>0.449</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3.900</t>
+          <t>4.200</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0.939</t>
+          <t>0.497</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>4.197</t>
+          <t>4.269</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0.627</t>
+          <t>0.649</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>4.200</t>
+          <t>4.269</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>0.525</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>3.985</t>
+          <t>4.615</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>0.506</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>4.169</t>
+          <t>4.365</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>0.642</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2.669</t>
+          <t>4.205</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>0.975</t>
+          <t>0.660</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>3.962</t>
+          <t>3.692</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>0.730</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>4.026</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>0.652</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>직위</t>
+          <t>귀하의종교는</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>t-value(p)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4.120</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>0.495</t>
-        </is>
-      </c>
+          <t>-1.744(.082)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3.709</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>0.749</t>
-        </is>
-      </c>
+          <t>-1.920(.056)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4.367</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>0.444</t>
-        </is>
-      </c>
+          <t>-0.396(.692)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4.246</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>0.601</t>
-        </is>
-      </c>
+          <t>-1.207(.228)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3.823</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>0.663</t>
-        </is>
-      </c>
+          <t>-0.945(.345)</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>4.079</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>0.759</t>
-        </is>
-      </c>
+          <t>-1.922(.055)</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>4.103</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>0.601</t>
-        </is>
-      </c>
+          <t>-1.387(.166)</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>4.040</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>0.529</t>
-        </is>
-      </c>
+          <t>-2.190*(.029)</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>4.057</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>0.657</t>
-        </is>
-      </c>
+          <t>-1.868(.063)</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2.526</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>0.825</t>
-        </is>
-      </c>
+          <t>-1.976*(.049)</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
-          <t>3.857</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>0.681</t>
-        </is>
-      </c>
+          <t>-1.049(.295)</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>-1.718(.087)</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>직위</t>
+          <t>귀하의성경통독횟수는</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3.896</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>0.425</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3.628</t>
+          <t>3.965</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>0.719</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4.137</t>
+          <t>4.333</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.806</t>
+          <t>0.599</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4.058</t>
+          <t>4.382</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.806</t>
+          <t>0.590</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3.744</t>
+          <t>3.967</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>0.585</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>4.055</t>
+          <t>3.910</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>0.634</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>3.992</t>
+          <t>3.913</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>0.604</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
+          <t>4.153</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>0.643</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>3.861</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>0.689</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
           <t>3.764</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>0.758</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>3.860</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>0.684</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>2.536</t>
-        </is>
-      </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>0.700</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>3.465</t>
+          <t>3.455</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>0.726</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>3.625</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>0.598</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>직위</t>
+          <t>귀하의성경통독횟수는</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>4.150</t>
+          <t>3.250</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.379</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3.695</t>
+          <t>4.051</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>0.681</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4.108</t>
+          <t>4.353</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>0.707</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4.166</t>
+          <t>4.412</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>0.629</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>3.667</t>
+          <t>4.035</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>0.687</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>4.066</t>
+          <t>3.967</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>0.717</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>4.050</t>
+          <t>4.051</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.605</t>
+          <t>0.745</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>3.864</t>
+          <t>4.221</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.580</t>
+          <t>0.808</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>3.984</t>
+          <t>4.044</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>0.715</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2.482</t>
+          <t>3.853</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.861</t>
+          <t>0.815</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>3.771</t>
+          <t>3.551</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.660</t>
+          <t>0.857</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>3.797</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>0.646</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>직위</t>
+          <t>귀하의성경통독횟수는</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>4.200</t>
+          <t>3.242</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.599</t>
+          <t>0.353</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3.914</t>
+          <t>3.929</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>0.661</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4.244</t>
+          <t>4.365</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.629</t>
+          <t>0.582</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4.147</t>
+          <t>4.376</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>0.581</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>3.707</t>
+          <t>4.052</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.908</t>
+          <t>0.646</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>4.272</t>
+          <t>3.933</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.680</t>
+          <t>0.622</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>4.050</t>
+          <t>4.058</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.853</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>3.914</t>
+          <t>4.245</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.715</t>
+          <t>0.619</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>4.114</t>
+          <t>4.078</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.670</t>
+          <t>0.617</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>3.036</t>
+          <t>3.813</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1.106</t>
+          <t>0.723</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>3.991</t>
+          <t>3.450</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>0.699</t>
+          <t>0.783</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>3.737</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>0.644</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>직위</t>
+          <t>귀하의성경통독횟수는</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4010,75 +4252,81 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.861(.117)</t>
+          <t>0.508†(.603)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.701(.150)</t>
+          <t>0.909(.404)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.349(.252)</t>
+          <t>0.080(.923)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.278(.279)</t>
+          <t>0.100(.905)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.717(.581)</t>
+          <t>0.500(.607)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.750(.559)</t>
+          <t>0.141(.868)</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.423(.792)</t>
+          <t>1.571(.209)</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.150(.333)</t>
+          <t>0.557(.573)</t>
         </is>
       </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1.533(.193)</t>
+          <t>3.230*(.041)</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2.193(.070)</t>
+          <t>0.259(.772)</t>
         </is>
       </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
-          <t>3.813**(.005)</t>
+          <t>0.466(.628)</t>
         </is>
       </c>
       <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>1.365(.257)</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>전문분야</t>
+          <t>귀하의교회직분은무엇입니까</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4088,119 +4336,129 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>4.084</t>
+          <t>3.240</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>0.390</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3.775</t>
+          <t>4.016</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>0.693</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4.166</t>
+          <t>4.373</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.677</t>
+          <t>0.614</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4.157</t>
+          <t>4.408</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>0.587</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>3.735</t>
+          <t>4.077</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>0.660</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>4.103</t>
+          <t>3.959</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>0.671</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>4.078</t>
+          <t>4.020</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>0.675</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3.873</t>
+          <t>4.276</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.640</t>
+          <t>0.703</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>3.999</t>
+          <t>4.042</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.599</t>
+          <t>0.696</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2.520</t>
+          <t>3.852</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>0.766</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>3.743</t>
+          <t>3.534</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>0.827</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>3.722</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>0.702</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>전문분야</t>
+          <t>귀하의교회직분은무엇입니까</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4210,517 +4468,475 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>4.207</t>
+          <t>3.222</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3.651</t>
+          <t>3.913</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>0.638</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4.182</t>
+          <t>4.416</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.640</t>
+          <t>0.567</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4.222</t>
+          <t>4.413</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>0.573</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>3.695</t>
+          <t>4.028</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>0.599</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>4.083</t>
+          <t>3.940</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>0.594</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>4.016</t>
+          <t>4.103</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>0.563</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>3.909</t>
+          <t>4.228</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>0.608</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>4.005</t>
+          <t>4.102</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>0.629</t>
+          <t>0.562</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2.677</t>
+          <t>3.858</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>0.896</t>
+          <t>0.685</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>3.826</t>
+          <t>3.493</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>0.754</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>3.785</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>0.566</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>전문분야</t>
+          <t>귀하의교회직분은무엇입니까</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>t-value(p)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-1.442(.151)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>3.241</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0.338</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.150(.252)</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>3.819</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0.695</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-0.195(.846)</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>4.117</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>0.636</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-0.826(.410)</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>4.202</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.577</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.413(.680)</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
+          <t>3.821</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0.689</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.231(.818)</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>3.723</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0.615</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.682(.496)</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr"/>
+          <t>3.835</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>0.572</t>
+        </is>
+      </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>-0.431(.667)</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr"/>
+          <t>3.979</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>0.608</t>
+        </is>
+      </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>-0.071(.944)</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
+          <t>3.771</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>0.636</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>-1.332(.185)</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr"/>
+          <t>3.461</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0.632</t>
+        </is>
+      </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>-0.930(.354)</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr"/>
+          <t>3.101</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>0.596</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>3.521</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>0.544</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>고용형태</t>
+          <t>귀하의교회직분은무엇입니까</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>4.108</t>
+          <t>3.289</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>0.452</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3.865</t>
+          <t>4.100</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.737</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4.243</t>
+          <t>4.267</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>0.704</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4.200</t>
+          <t>4.300</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>0.775</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>3.843</t>
+          <t>4.253</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>0.635</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>4.181</t>
+          <t>4.233</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.599</t>
+          <t>0.684</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>4.065</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.693</t>
+          <t>0.773</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>3.876</t>
+          <t>4.333</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>0.617</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>4.041</t>
+          <t>4.033</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>0.580</t>
+          <t>0.860</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2.710</t>
+          <t>3.867</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>0.984</t>
+          <t>0.915</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>3.841</t>
+          <t>3.517</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>0.677</t>
+          <t>0.884</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>3.800</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>0.749</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>고용형태</t>
+          <t>귀하의교회직분은무엇입니까</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>F-value(p)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4.127</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>0.663</t>
-        </is>
-      </c>
+          <t>0.191(.902)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3.671</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>0.817</t>
-        </is>
-      </c>
+          <t>1.595(.190)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4.132</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>0.679</t>
-        </is>
-      </c>
+          <t>3.193*(.024)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4.163</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>0.686</t>
-        </is>
-      </c>
+          <t>1.842(.139)</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>3.659</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>0.771</t>
-        </is>
-      </c>
+          <t>2.612(.051)</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>4.052</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>0.708</t>
-        </is>
-      </c>
+          <t>2.939*(.033)</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>4.057</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>0.697</t>
-        </is>
-      </c>
+          <t>2.711†(.053)</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>3.887</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>0.640</t>
-        </is>
-      </c>
+          <t>2.965*†(.039)</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
-          <t>3.979</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>0.621</t>
-        </is>
-      </c>
+          <t>3.389*†(.024)</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2.489</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>0.909</t>
-        </is>
-      </c>
+          <t>5.110**†(.003)</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
-          <t>3.728</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>0.714</t>
-        </is>
-      </c>
+          <t>6.028**†(.001)</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2.822*†(.047)</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
-        <is>
-          <t>고용형태</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>t-value(p)</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>-0.217(.828)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2.007*(.046)</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>1.399(.163)</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>0.469(.639)</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>2.001*(.047)</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>1.649(.100)</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>0.092(.927)</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>-0.135(.892)</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>0.852(.395)</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>1.873(.063)</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>1.334(.183)</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
         <is>
           <t>* p&lt;.05, ** p&lt;.01, *** p&lt;.001</t>
         </is>
